--- a/d_energy/Сonsumption plan Data_frame_1.xlsx
+++ b/d_energy/Сonsumption plan Data_frame_1.xlsx
@@ -546,10 +546,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C3" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D3" s="5">
         <v>30</v>
@@ -577,10 +577,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C4" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D4" s="5">
         <v>24</v>
@@ -608,10 +608,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C5" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D5" s="5">
         <v>39</v>
@@ -657,7 +657,7 @@
         <v>43</v>
       </c>
       <c r="H6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
@@ -688,7 +688,7 @@
         <v>37</v>
       </c>
       <c r="H7" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" s="5"/>
       <c r="J7" s="5"/>
@@ -719,7 +719,7 @@
         <v>52</v>
       </c>
       <c r="H8" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" s="5"/>
       <c r="J8" s="5"/>
@@ -732,10 +732,10 @@
         <v>7</v>
       </c>
       <c r="B9" s="3">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3">
         <v>2</v>
-      </c>
-      <c r="C9" s="3">
-        <v>0</v>
       </c>
       <c r="D9" s="5">
         <v>32</v>
@@ -797,7 +797,7 @@
         <v>0</v>
       </c>
       <c r="C11" s="3">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="D11" s="5">
         <v>46</v>
@@ -828,7 +828,7 @@
         <v>0</v>
       </c>
       <c r="C12" s="3">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="D12" s="5">
         <v>58</v>
@@ -856,10 +856,10 @@
         <v>11</v>
       </c>
       <c r="B13" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C13" s="3">
-        <v>10</v>
+        <v>62</v>
       </c>
       <c r="D13" s="5">
         <v>59</v>
@@ -887,10 +887,10 @@
         <v>12</v>
       </c>
       <c r="B14" s="3">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C14" s="3">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="D14" s="5">
         <v>47</v>
@@ -918,10 +918,10 @@
         <v>13</v>
       </c>
       <c r="B15" s="3">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C15" s="3">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D15" s="5">
         <v>49</v>
@@ -980,10 +980,10 @@
         <v>15</v>
       </c>
       <c r="B17" s="3">
+        <v>20</v>
+      </c>
+      <c r="C17" s="3">
         <v>26</v>
-      </c>
-      <c r="C17" s="3">
-        <v>20</v>
       </c>
       <c r="D17" s="5">
         <v>52</v>
@@ -1011,10 +1011,10 @@
         <v>16</v>
       </c>
       <c r="B18" s="3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C18" s="3">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D18" s="5">
         <v>66</v>
@@ -1042,10 +1042,10 @@
         <v>17</v>
       </c>
       <c r="B19" s="3">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="C19" s="3">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="D19" s="5">
         <v>65</v>
@@ -1073,10 +1073,10 @@
         <v>18</v>
       </c>
       <c r="B20" s="3">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="C20" s="3">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="D20" s="5">
         <v>58</v>
@@ -1104,10 +1104,10 @@
         <v>19</v>
       </c>
       <c r="B21" s="3">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="C21" s="3">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="D21" s="5">
         <v>70</v>
@@ -1138,7 +1138,7 @@
         <v>45</v>
       </c>
       <c r="C22" s="3">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="D22" s="5">
         <v>72</v>
@@ -1166,10 +1166,10 @@
         <v>21</v>
       </c>
       <c r="B23" s="3">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C23" s="3">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D23" s="5">
         <v>79</v>
@@ -1197,10 +1197,10 @@
         <v>22</v>
       </c>
       <c r="B24" s="3">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="C24" s="3">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="D24" s="5">
         <v>75</v>
@@ -1228,10 +1228,10 @@
         <v>23</v>
       </c>
       <c r="B25" s="3">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="C25" s="3">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="D25" s="5">
         <v>69</v>
@@ -1259,22 +1259,22 @@
         <v>24</v>
       </c>
       <c r="B26" s="3">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C26" s="3">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="D26" s="5">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="E26" s="5">
-        <v>41</v>
+        <v>99</v>
       </c>
       <c r="F26" s="5">
-        <v>38</v>
+        <v>99</v>
       </c>
       <c r="G26" s="5">
-        <v>49</v>
+        <v>99</v>
       </c>
       <c r="H26" s="5">
         <v>0</v>
@@ -1290,22 +1290,22 @@
         <v>25</v>
       </c>
       <c r="B27" s="3">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C27" s="3">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="D27" s="5">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="E27" s="5">
-        <v>52</v>
+        <v>99</v>
       </c>
       <c r="F27" s="5">
-        <v>47</v>
+        <v>99</v>
       </c>
       <c r="G27" s="5">
-        <v>51</v>
+        <v>99</v>
       </c>
       <c r="H27" s="5">
         <v>0</v>
@@ -1321,22 +1321,22 @@
         <v>26</v>
       </c>
       <c r="B28" s="3">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="C28" s="3">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D28" s="7">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="E28" s="7">
-        <v>43</v>
+        <v>99</v>
       </c>
       <c r="F28" s="7">
-        <v>29</v>
+        <v>99</v>
       </c>
       <c r="G28" s="7">
-        <v>62</v>
+        <v>99</v>
       </c>
       <c r="H28" s="7">
         <v>0</v>
@@ -1352,22 +1352,22 @@
         <v>27</v>
       </c>
       <c r="B29" s="3">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="C29" s="3">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="D29" s="7">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="E29" s="7">
-        <v>45</v>
+        <v>99</v>
       </c>
       <c r="F29" s="7">
-        <v>29</v>
+        <v>99</v>
       </c>
       <c r="G29" s="7">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="H29" s="7">
         <v>0</v>
@@ -1383,22 +1383,22 @@
         <v>28</v>
       </c>
       <c r="B30" s="3">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="C30" s="3">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="D30" s="7">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="E30" s="7">
-        <v>47</v>
+        <v>99</v>
       </c>
       <c r="F30" s="7">
-        <v>43</v>
+        <v>99</v>
       </c>
       <c r="G30" s="7">
-        <v>56</v>
+        <v>99</v>
       </c>
       <c r="H30" s="7">
         <v>0</v>
@@ -1414,22 +1414,22 @@
         <v>29</v>
       </c>
       <c r="B31" s="3">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="C31" s="3">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="D31" s="7">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="E31" s="7">
-        <v>55</v>
+        <v>99</v>
       </c>
       <c r="F31" s="7">
-        <v>30</v>
+        <v>99</v>
       </c>
       <c r="G31" s="7">
-        <v>55</v>
+        <v>99</v>
       </c>
       <c r="H31" s="7">
         <v>0</v>
@@ -1445,22 +1445,22 @@
         <v>30</v>
       </c>
       <c r="B32" s="3">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="C32" s="3">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="D32" s="7">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E32" s="7">
-        <v>52</v>
+        <v>99</v>
       </c>
       <c r="F32" s="7">
-        <v>29</v>
+        <v>99</v>
       </c>
       <c r="G32" s="7">
-        <v>60</v>
+        <v>99</v>
       </c>
       <c r="H32" s="7">
         <v>0</v>
@@ -1476,22 +1476,22 @@
         <v>31</v>
       </c>
       <c r="B33" s="3">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="C33" s="3">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="D33" s="7">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="E33" s="7">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="F33" s="7">
-        <v>29</v>
+        <v>99</v>
       </c>
       <c r="G33" s="7">
-        <v>63</v>
+        <v>99</v>
       </c>
       <c r="H33" s="7">
         <v>0</v>
@@ -1507,22 +1507,22 @@
         <v>32</v>
       </c>
       <c r="B34" s="3">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="C34" s="3">
         <v>35</v>
       </c>
       <c r="D34" s="7">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="E34" s="7">
-        <v>60</v>
+        <v>99</v>
       </c>
       <c r="F34" s="7">
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="G34" s="7">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="H34" s="7">
         <v>0</v>
@@ -1538,22 +1538,22 @@
         <v>33</v>
       </c>
       <c r="B35" s="3">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="C35" s="3">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="D35" s="7">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="E35" s="7">
-        <v>47</v>
+        <v>99</v>
       </c>
       <c r="F35" s="7">
-        <v>31</v>
+        <v>99</v>
       </c>
       <c r="G35" s="7">
-        <v>57</v>
+        <v>99</v>
       </c>
       <c r="H35" s="7">
         <v>0</v>
@@ -1569,22 +1569,22 @@
         <v>34</v>
       </c>
       <c r="B36" s="3">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="C36" s="3">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="D36" s="7">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="E36" s="7">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="F36" s="7">
-        <v>30</v>
+        <v>99</v>
       </c>
       <c r="G36" s="7">
-        <v>49</v>
+        <v>99</v>
       </c>
       <c r="H36" s="7">
         <v>0</v>
@@ -1600,22 +1600,22 @@
         <v>35</v>
       </c>
       <c r="B37" s="3">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="C37" s="3">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="D37" s="7">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="E37" s="7">
-        <v>44</v>
+        <v>99</v>
       </c>
       <c r="F37" s="7">
-        <v>29</v>
+        <v>99</v>
       </c>
       <c r="G37" s="7">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="H37" s="7">
         <v>0</v>
@@ -1631,22 +1631,22 @@
         <v>36</v>
       </c>
       <c r="B38" s="3">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="C38" s="3">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="D38" s="7">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="E38" s="7">
-        <v>47</v>
+        <v>99</v>
       </c>
       <c r="F38" s="7">
-        <v>34</v>
+        <v>99</v>
       </c>
       <c r="G38" s="7">
-        <v>50</v>
+        <v>99</v>
       </c>
       <c r="H38" s="7">
         <v>0</v>
@@ -1662,22 +1662,22 @@
         <v>37</v>
       </c>
       <c r="B39" s="3">
+        <v>24</v>
+      </c>
+      <c r="C39" s="3">
         <v>46</v>
       </c>
-      <c r="C39" s="3">
-        <v>24</v>
-      </c>
       <c r="D39" s="7">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="E39" s="7">
-        <v>57</v>
+        <v>99</v>
       </c>
       <c r="F39" s="7">
-        <v>38</v>
+        <v>99</v>
       </c>
       <c r="G39" s="7">
-        <v>60</v>
+        <v>99</v>
       </c>
       <c r="H39" s="7">
         <v>0</v>
@@ -1693,22 +1693,22 @@
         <v>38</v>
       </c>
       <c r="B40" s="3">
+        <v>24</v>
+      </c>
+      <c r="C40" s="3">
         <v>37</v>
       </c>
-      <c r="C40" s="3">
-        <v>24</v>
-      </c>
       <c r="D40" s="7">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="E40" s="7">
-        <v>56</v>
+        <v>99</v>
       </c>
       <c r="F40" s="7">
-        <v>46</v>
+        <v>99</v>
       </c>
       <c r="G40" s="7">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="H40" s="7">
         <v>0</v>
@@ -1724,22 +1724,22 @@
         <v>39</v>
       </c>
       <c r="B41" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C41" s="3">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D41" s="7">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="E41" s="7">
-        <v>46</v>
+        <v>99</v>
       </c>
       <c r="F41" s="7">
-        <v>43</v>
+        <v>99</v>
       </c>
       <c r="G41" s="7">
-        <v>50</v>
+        <v>99</v>
       </c>
       <c r="H41" s="7">
         <v>0</v>
@@ -1755,22 +1755,22 @@
         <v>40</v>
       </c>
       <c r="B42" s="3">
+        <v>36</v>
+      </c>
+      <c r="C42" s="3">
         <v>21</v>
       </c>
-      <c r="C42" s="3">
-        <v>36</v>
-      </c>
       <c r="D42" s="7">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="E42" s="7">
-        <v>55</v>
+        <v>99</v>
       </c>
       <c r="F42" s="7">
-        <v>55</v>
+        <v>99</v>
       </c>
       <c r="G42" s="7">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="H42" s="7">
         <v>0</v>
@@ -1786,22 +1786,22 @@
         <v>41</v>
       </c>
       <c r="B43" s="3">
+        <v>36</v>
+      </c>
+      <c r="C43" s="3">
         <v>23</v>
       </c>
-      <c r="C43" s="3">
-        <v>36</v>
-      </c>
       <c r="D43" s="7">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="E43" s="7">
-        <v>42</v>
+        <v>99</v>
       </c>
       <c r="F43" s="7">
-        <v>36</v>
+        <v>99</v>
       </c>
       <c r="G43" s="7">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="H43" s="7">
         <v>0</v>
@@ -1817,22 +1817,22 @@
         <v>42</v>
       </c>
       <c r="B44" s="3">
+        <v>36</v>
+      </c>
+      <c r="C44" s="3">
         <v>27</v>
       </c>
-      <c r="C44" s="3">
-        <v>36</v>
-      </c>
       <c r="D44" s="7">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="E44" s="7">
-        <v>47</v>
+        <v>99</v>
       </c>
       <c r="F44" s="7">
-        <v>52</v>
+        <v>99</v>
       </c>
       <c r="G44" s="7">
-        <v>57</v>
+        <v>99</v>
       </c>
       <c r="H44" s="7">
         <v>0</v>
@@ -1848,22 +1848,22 @@
         <v>43</v>
       </c>
       <c r="B45" s="3">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C45" s="3">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="D45" s="7">
-        <v>64</v>
+        <v>99</v>
       </c>
       <c r="E45" s="7">
-        <v>46</v>
+        <v>99</v>
       </c>
       <c r="F45" s="7">
-        <v>45</v>
+        <v>99</v>
       </c>
       <c r="G45" s="7">
-        <v>52</v>
+        <v>99</v>
       </c>
       <c r="H45" s="7">
         <v>0</v>
@@ -1879,22 +1879,22 @@
         <v>44</v>
       </c>
       <c r="B46" s="3">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="C46" s="3">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="D46" s="7">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="E46" s="7">
-        <v>48</v>
+        <v>99</v>
       </c>
       <c r="F46" s="7">
-        <v>42</v>
+        <v>99</v>
       </c>
       <c r="G46" s="7">
-        <v>52</v>
+        <v>99</v>
       </c>
       <c r="H46" s="7">
         <v>0</v>
@@ -1910,22 +1910,22 @@
         <v>45</v>
       </c>
       <c r="B47" s="3">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="C47" s="3">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="D47" s="7">
-        <v>66</v>
+        <v>99</v>
       </c>
       <c r="E47" s="7">
-        <v>45</v>
+        <v>99</v>
       </c>
       <c r="F47" s="7">
-        <v>49</v>
+        <v>99</v>
       </c>
       <c r="G47" s="7">
-        <v>38</v>
+        <v>99</v>
       </c>
       <c r="H47" s="7">
         <v>0</v>
@@ -1941,22 +1941,22 @@
         <v>46</v>
       </c>
       <c r="B48" s="3">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="C48" s="3">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="D48" s="7">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="E48" s="7">
-        <v>57</v>
+        <v>99</v>
       </c>
       <c r="F48" s="7">
-        <v>45</v>
+        <v>99</v>
       </c>
       <c r="G48" s="7">
-        <v>51</v>
+        <v>99</v>
       </c>
       <c r="H48" s="7">
         <v>0</v>
@@ -1972,22 +1972,22 @@
         <v>47</v>
       </c>
       <c r="B49" s="3">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="C49" s="3">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="D49" s="7">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="E49" s="7">
-        <v>48</v>
+        <v>99</v>
       </c>
       <c r="F49" s="7">
-        <v>48</v>
+        <v>99</v>
       </c>
       <c r="G49" s="7">
-        <v>49</v>
+        <v>99</v>
       </c>
       <c r="H49" s="7">
         <v>0</v>
@@ -2003,22 +2003,22 @@
         <v>48</v>
       </c>
       <c r="B50" s="3">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="C50" s="3">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="D50" s="7">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="E50" s="7">
-        <v>47</v>
+        <v>99</v>
       </c>
       <c r="F50" s="7">
-        <v>63</v>
+        <v>99</v>
       </c>
       <c r="G50" s="7">
-        <v>45</v>
+        <v>99</v>
       </c>
       <c r="H50" s="7">
         <v>0</v>
@@ -2034,22 +2034,22 @@
         <v>49</v>
       </c>
       <c r="B51" s="3">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="C51" s="3">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="D51" s="7">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="E51" s="7">
-        <v>55</v>
+        <v>99</v>
       </c>
       <c r="F51" s="7">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="G51" s="7">
-        <v>50</v>
+        <v>99</v>
       </c>
       <c r="H51" s="7">
         <v>0</v>
@@ -2065,22 +2065,22 @@
         <v>50</v>
       </c>
       <c r="B52" s="3">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="C52" s="3">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="D52" s="7">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="E52" s="7">
-        <v>50</v>
+        <v>99</v>
       </c>
       <c r="F52" s="7">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="G52" s="7">
-        <v>51</v>
+        <v>99</v>
       </c>
       <c r="H52" s="7">
         <v>0</v>
@@ -2096,22 +2096,22 @@
         <v>51</v>
       </c>
       <c r="B53" s="3">
+        <v>32</v>
+      </c>
+      <c r="C53" s="3">
         <v>3</v>
       </c>
-      <c r="C53" s="3">
-        <v>32</v>
-      </c>
       <c r="D53" s="7">
-        <v>55</v>
+        <v>99</v>
       </c>
       <c r="E53" s="7">
-        <v>53</v>
+        <v>99</v>
       </c>
       <c r="F53" s="7">
-        <v>62</v>
+        <v>99</v>
       </c>
       <c r="G53" s="7">
-        <v>37</v>
+        <v>99</v>
       </c>
       <c r="H53" s="7">
         <v>0</v>
@@ -2127,22 +2127,22 @@
         <v>52</v>
       </c>
       <c r="B54" s="3">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="C54" s="3">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="D54" s="7">
-        <v>55</v>
+        <v>99</v>
       </c>
       <c r="E54" s="7">
-        <v>48</v>
+        <v>99</v>
       </c>
       <c r="F54" s="7">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="G54" s="7">
-        <v>41</v>
+        <v>99</v>
       </c>
       <c r="H54" s="7">
         <v>0</v>
@@ -2158,22 +2158,22 @@
         <v>53</v>
       </c>
       <c r="B55" s="3">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="C55" s="3">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="D55" s="7">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="E55" s="7">
-        <v>41</v>
+        <v>99</v>
       </c>
       <c r="F55" s="7">
-        <v>56</v>
+        <v>99</v>
       </c>
       <c r="G55" s="7">
-        <v>34</v>
+        <v>99</v>
       </c>
       <c r="H55" s="7">
         <v>0</v>
@@ -2189,22 +2189,22 @@
         <v>54</v>
       </c>
       <c r="B56" s="3">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="C56" s="3">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="D56" s="7">
-        <v>53</v>
+        <v>99</v>
       </c>
       <c r="E56" s="7">
-        <v>51</v>
+        <v>99</v>
       </c>
       <c r="F56" s="7">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="G56" s="7">
-        <v>34</v>
+        <v>99</v>
       </c>
       <c r="H56" s="7">
         <v>0</v>
@@ -2220,22 +2220,22 @@
         <v>55</v>
       </c>
       <c r="B57" s="3">
+        <v>22</v>
+      </c>
+      <c r="C57" s="3">
         <v>2</v>
       </c>
-      <c r="C57" s="3">
-        <v>22</v>
-      </c>
       <c r="D57" s="7">
-        <v>68</v>
+        <v>99</v>
       </c>
       <c r="E57" s="7">
-        <v>44</v>
+        <v>99</v>
       </c>
       <c r="F57" s="7">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="G57" s="7">
-        <v>35</v>
+        <v>99</v>
       </c>
       <c r="H57" s="7">
         <v>0</v>
@@ -2251,22 +2251,22 @@
         <v>56</v>
       </c>
       <c r="B58" s="3">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="C58" s="3">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="D58" s="7">
-        <v>55</v>
+        <v>99</v>
       </c>
       <c r="E58" s="7">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="F58" s="7">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="G58" s="7">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="H58" s="7">
         <v>0</v>
@@ -2282,22 +2282,22 @@
         <v>57</v>
       </c>
       <c r="B59" s="3">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="C59" s="3">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="D59" s="7">
-        <v>56</v>
+        <v>99</v>
       </c>
       <c r="E59" s="7">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="F59" s="7">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="G59" s="7">
-        <v>38</v>
+        <v>99</v>
       </c>
       <c r="H59" s="7">
         <v>0</v>
@@ -2313,22 +2313,22 @@
         <v>58</v>
       </c>
       <c r="B60" s="3">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="C60" s="3">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D60" s="7">
-        <v>51</v>
+        <v>99</v>
       </c>
       <c r="E60" s="7">
-        <v>53</v>
+        <v>99</v>
       </c>
       <c r="F60" s="7">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="G60" s="7">
-        <v>37</v>
+        <v>99</v>
       </c>
       <c r="H60" s="7">
         <v>0</v>
@@ -2344,22 +2344,22 @@
         <v>59</v>
       </c>
       <c r="B61" s="3">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C61" s="3">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D61" s="7">
-        <v>42</v>
+        <v>99</v>
       </c>
       <c r="E61" s="7">
-        <v>41</v>
+        <v>99</v>
       </c>
       <c r="F61" s="7">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="G61" s="7">
-        <v>24</v>
+        <v>99</v>
       </c>
       <c r="H61" s="7">
         <v>0</v>
@@ -2375,22 +2375,22 @@
         <v>60</v>
       </c>
       <c r="B62" s="3">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="C62" s="3">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D62" s="7">
-        <v>46</v>
+        <v>99</v>
       </c>
       <c r="E62" s="7">
-        <v>56</v>
+        <v>99</v>
       </c>
       <c r="F62" s="7">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="G62" s="7">
-        <v>30</v>
+        <v>99</v>
       </c>
       <c r="H62" s="7">
         <v>0</v>
@@ -2406,22 +2406,22 @@
         <v>61</v>
       </c>
       <c r="B63" s="3">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="C63" s="3">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="D63" s="7">
-        <v>43</v>
+        <v>99</v>
       </c>
       <c r="E63" s="7">
-        <v>47</v>
+        <v>99</v>
       </c>
       <c r="F63" s="7">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="G63" s="7">
-        <v>28</v>
+        <v>99</v>
       </c>
       <c r="H63" s="7">
         <v>0</v>
@@ -2437,22 +2437,22 @@
         <v>62</v>
       </c>
       <c r="B64" s="3">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="C64" s="3">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D64" s="7">
-        <v>46</v>
+        <v>99</v>
       </c>
       <c r="E64" s="7">
-        <v>57</v>
+        <v>99</v>
       </c>
       <c r="F64" s="7">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="G64" s="7">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="H64" s="7">
         <v>0</v>
@@ -2468,22 +2468,22 @@
         <v>63</v>
       </c>
       <c r="B65" s="3">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C65" s="3">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="D65" s="7">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="E65" s="7">
-        <v>51</v>
+        <v>99</v>
       </c>
       <c r="F65" s="7">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="G65" s="7">
-        <v>27</v>
+        <v>99</v>
       </c>
       <c r="H65" s="7">
         <v>0</v>
@@ -2499,22 +2499,22 @@
         <v>64</v>
       </c>
       <c r="B66" s="3">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C66" s="3">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="D66" s="7">
-        <v>56</v>
+        <v>99</v>
       </c>
       <c r="E66" s="7">
-        <v>57</v>
+        <v>99</v>
       </c>
       <c r="F66" s="7">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="G66" s="7">
-        <v>28</v>
+        <v>99</v>
       </c>
       <c r="H66" s="7">
         <v>0</v>
@@ -2530,22 +2530,22 @@
         <v>65</v>
       </c>
       <c r="B67" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C67" s="3">
-        <v>9</v>
+        <v>70</v>
       </c>
       <c r="D67" s="7">
-        <v>42</v>
+        <v>99</v>
       </c>
       <c r="E67" s="7">
-        <v>50</v>
+        <v>99</v>
       </c>
       <c r="F67" s="7">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="G67" s="7">
-        <v>37</v>
+        <v>99</v>
       </c>
       <c r="H67" s="7">
         <v>0</v>
@@ -2561,25 +2561,25 @@
         <v>66</v>
       </c>
       <c r="B68" s="3">
+        <v>11</v>
+      </c>
+      <c r="C68" s="3">
+        <v>55</v>
+      </c>
+      <c r="D68" s="7">
+        <v>99</v>
+      </c>
+      <c r="E68" s="7">
+        <v>99</v>
+      </c>
+      <c r="F68" s="7">
+        <v>99</v>
+      </c>
+      <c r="G68" s="7">
+        <v>99</v>
+      </c>
+      <c r="H68" s="7">
         <v>1</v>
-      </c>
-      <c r="C68" s="3">
-        <v>11</v>
-      </c>
-      <c r="D68" s="7">
-        <v>39</v>
-      </c>
-      <c r="E68" s="7">
-        <v>40</v>
-      </c>
-      <c r="F68" s="7">
-        <v>76</v>
-      </c>
-      <c r="G68" s="7">
-        <v>27</v>
-      </c>
-      <c r="H68" s="7">
-        <v>0</v>
       </c>
       <c r="I68" s="7"/>
       <c r="J68" s="7"/>
@@ -2592,25 +2592,25 @@
         <v>67</v>
       </c>
       <c r="B69" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C69" s="3">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="D69" s="7">
-        <v>38</v>
+        <v>99</v>
       </c>
       <c r="E69" s="7">
-        <v>53</v>
+        <v>99</v>
       </c>
       <c r="F69" s="7">
-        <v>66</v>
+        <v>99</v>
       </c>
       <c r="G69" s="7">
-        <v>35</v>
+        <v>99</v>
       </c>
       <c r="H69" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I69" s="7"/>
       <c r="J69" s="7"/>
@@ -2623,25 +2623,25 @@
         <v>68</v>
       </c>
       <c r="B70" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C70" s="3">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="D70" s="7">
-        <v>50</v>
+        <v>99</v>
       </c>
       <c r="E70" s="7">
-        <v>40</v>
+        <v>99</v>
       </c>
       <c r="F70" s="7">
-        <v>68</v>
+        <v>99</v>
       </c>
       <c r="G70" s="7">
-        <v>47</v>
+        <v>99</v>
       </c>
       <c r="H70" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I70" s="7"/>
       <c r="J70" s="7"/>
@@ -2654,25 +2654,25 @@
         <v>69</v>
       </c>
       <c r="B71" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C71" s="3">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D71" s="7">
-        <v>47</v>
+        <v>99</v>
       </c>
       <c r="E71" s="7">
-        <v>43</v>
+        <v>99</v>
       </c>
       <c r="F71" s="7">
-        <v>62</v>
+        <v>99</v>
       </c>
       <c r="G71" s="7">
-        <v>29</v>
+        <v>99</v>
       </c>
       <c r="H71" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I71" s="7"/>
       <c r="J71" s="7"/>
@@ -2685,25 +2685,25 @@
         <v>70</v>
       </c>
       <c r="B72" s="3">
+        <v>3</v>
+      </c>
+      <c r="C72" s="3">
+        <v>15</v>
+      </c>
+      <c r="D72" s="7">
+        <v>99</v>
+      </c>
+      <c r="E72" s="7">
+        <v>99</v>
+      </c>
+      <c r="F72" s="7">
+        <v>99</v>
+      </c>
+      <c r="G72" s="7">
+        <v>99</v>
+      </c>
+      <c r="H72" s="7">
         <v>1</v>
-      </c>
-      <c r="C72" s="3">
-        <v>3</v>
-      </c>
-      <c r="D72" s="7">
-        <v>36</v>
-      </c>
-      <c r="E72" s="7">
-        <v>60</v>
-      </c>
-      <c r="F72" s="7">
-        <v>62</v>
-      </c>
-      <c r="G72" s="7">
-        <v>38</v>
-      </c>
-      <c r="H72" s="7">
-        <v>0</v>
       </c>
       <c r="I72" s="7"/>
       <c r="J72" s="7"/>
@@ -2716,25 +2716,25 @@
         <v>71</v>
       </c>
       <c r="B73" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C73" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D73" s="7">
-        <v>44</v>
+        <v>99</v>
       </c>
       <c r="E73" s="7">
-        <v>55</v>
+        <v>99</v>
       </c>
       <c r="F73" s="7">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="G73" s="7">
-        <v>38</v>
+        <v>99</v>
       </c>
       <c r="H73" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I73" s="7"/>
       <c r="J73" s="7"/>
@@ -2747,25 +2747,25 @@
         <v>72</v>
       </c>
       <c r="B74" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C74" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D74" s="7">
-        <v>38</v>
+        <v>99</v>
       </c>
       <c r="E74" s="7">
-        <v>48</v>
+        <v>99</v>
       </c>
       <c r="F74" s="7">
-        <v>60</v>
+        <v>99</v>
       </c>
       <c r="G74" s="7">
-        <v>50</v>
+        <v>99</v>
       </c>
       <c r="H74" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I74" s="7"/>
       <c r="J74" s="7"/>
@@ -2778,25 +2778,25 @@
         <v>73</v>
       </c>
       <c r="B75" s="3">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C75" s="3">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D75" s="7">
-        <v>37</v>
+        <v>99</v>
       </c>
       <c r="E75" s="7">
-        <v>56</v>
+        <v>99</v>
       </c>
       <c r="F75" s="7">
-        <v>64</v>
+        <v>99</v>
       </c>
       <c r="G75" s="7">
-        <v>32</v>
+        <v>99</v>
       </c>
       <c r="H75" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I75" s="7"/>
       <c r="J75" s="7"/>
@@ -2809,25 +2809,25 @@
         <v>74</v>
       </c>
       <c r="B76" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C76" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D76" s="7">
-        <v>48</v>
+        <v>99</v>
       </c>
       <c r="E76" s="7">
-        <v>48</v>
+        <v>99</v>
       </c>
       <c r="F76" s="7">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="G76" s="7">
-        <v>36</v>
+        <v>99</v>
       </c>
       <c r="H76" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I76" s="7"/>
       <c r="J76" s="7"/>
@@ -2840,25 +2840,25 @@
         <v>75</v>
       </c>
       <c r="B77" s="3">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C77" s="3">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D77" s="7">
-        <v>43</v>
+        <v>99</v>
       </c>
       <c r="E77" s="7">
-        <v>51</v>
+        <v>99</v>
       </c>
       <c r="F77" s="7">
-        <v>68</v>
+        <v>99</v>
       </c>
       <c r="G77" s="7">
-        <v>41</v>
+        <v>99</v>
       </c>
       <c r="H77" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I77" s="7"/>
       <c r="J77" s="7"/>
@@ -2871,22 +2871,22 @@
         <v>76</v>
       </c>
       <c r="B78" s="3">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C78" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D78" s="7">
-        <v>35</v>
+        <v>99</v>
       </c>
       <c r="E78" s="7">
-        <v>48</v>
+        <v>99</v>
       </c>
       <c r="F78" s="7">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="G78" s="7">
-        <v>37</v>
+        <v>99</v>
       </c>
       <c r="H78" s="7">
         <v>0</v>
@@ -2902,22 +2902,22 @@
         <v>77</v>
       </c>
       <c r="B79" s="3">
+        <v>2</v>
+      </c>
+      <c r="C79" s="3">
         <v>18</v>
       </c>
-      <c r="C79" s="3">
-        <v>2</v>
-      </c>
       <c r="D79" s="7">
-        <v>35</v>
+        <v>99</v>
       </c>
       <c r="E79" s="7">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="F79" s="7">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="G79" s="7">
-        <v>49</v>
+        <v>99</v>
       </c>
       <c r="H79" s="7">
         <v>0</v>
@@ -2933,22 +2933,22 @@
         <v>78</v>
       </c>
       <c r="B80" s="3">
+        <v>2</v>
+      </c>
+      <c r="C80" s="3">
         <v>20</v>
       </c>
-      <c r="C80" s="3">
-        <v>2</v>
-      </c>
       <c r="D80" s="7">
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="E80" s="7">
-        <v>46</v>
+        <v>99</v>
       </c>
       <c r="F80" s="7">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="G80" s="7">
-        <v>57</v>
+        <v>99</v>
       </c>
       <c r="H80" s="7">
         <v>0</v>
@@ -2964,22 +2964,22 @@
         <v>79</v>
       </c>
       <c r="B81" s="3">
+        <v>1</v>
+      </c>
+      <c r="C81" s="3">
         <v>20</v>
       </c>
-      <c r="C81" s="3">
-        <v>1</v>
-      </c>
       <c r="D81" s="7">
-        <v>30</v>
+        <v>99</v>
       </c>
       <c r="E81" s="7">
-        <v>57</v>
+        <v>99</v>
       </c>
       <c r="F81" s="7">
-        <v>67</v>
+        <v>99</v>
       </c>
       <c r="G81" s="7">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="H81" s="7">
         <v>0</v>
@@ -2995,22 +2995,22 @@
         <v>80</v>
       </c>
       <c r="B82" s="3">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="C82" s="3">
-        <v>2</v>
+        <v>55</v>
       </c>
       <c r="D82" s="7">
-        <v>30</v>
+        <v>99</v>
       </c>
       <c r="E82" s="7">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="F82" s="7">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="G82" s="7">
-        <v>46</v>
+        <v>99</v>
       </c>
       <c r="H82" s="7">
         <v>0</v>
@@ -3026,22 +3026,22 @@
         <v>81</v>
       </c>
       <c r="B83" s="3">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="C83" s="3">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="D83" s="7">
-        <v>32</v>
+        <v>99</v>
       </c>
       <c r="E83" s="7">
-        <v>48</v>
+        <v>99</v>
       </c>
       <c r="F83" s="7">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="G83" s="7">
-        <v>43</v>
+        <v>99</v>
       </c>
       <c r="H83" s="7">
         <v>0</v>
@@ -3057,22 +3057,22 @@
         <v>82</v>
       </c>
       <c r="B84" s="3">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="C84" s="3">
-        <v>8</v>
+        <v>90</v>
       </c>
       <c r="D84" s="7">
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="E84" s="7">
-        <v>48</v>
+        <v>99</v>
       </c>
       <c r="F84" s="7">
-        <v>63</v>
+        <v>99</v>
       </c>
       <c r="G84" s="7">
-        <v>49</v>
+        <v>99</v>
       </c>
       <c r="H84" s="7">
         <v>0</v>
@@ -3088,22 +3088,22 @@
         <v>83</v>
       </c>
       <c r="B85" s="3">
+        <v>1</v>
+      </c>
+      <c r="C85" s="3">
         <v>50</v>
       </c>
-      <c r="C85" s="3">
-        <v>1</v>
-      </c>
       <c r="D85" s="7">
-        <v>29</v>
+        <v>99</v>
       </c>
       <c r="E85" s="7">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="F85" s="7">
-        <v>62</v>
+        <v>99</v>
       </c>
       <c r="G85" s="7">
-        <v>44</v>
+        <v>99</v>
       </c>
       <c r="H85" s="7">
         <v>0</v>
@@ -3119,22 +3119,22 @@
         <v>84</v>
       </c>
       <c r="B86" s="3">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="C86" s="3">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="D86" s="7">
-        <v>28</v>
+        <v>99</v>
       </c>
       <c r="E86" s="7">
-        <v>45</v>
+        <v>99</v>
       </c>
       <c r="F86" s="7">
-        <v>47</v>
+        <v>99</v>
       </c>
       <c r="G86" s="7">
-        <v>57</v>
+        <v>99</v>
       </c>
       <c r="H86" s="7">
         <v>0</v>
@@ -3150,22 +3150,22 @@
         <v>85</v>
       </c>
       <c r="B87" s="3">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="C87" s="3">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="D87" s="7">
-        <v>36</v>
+        <v>99</v>
       </c>
       <c r="E87" s="7">
-        <v>55</v>
+        <v>99</v>
       </c>
       <c r="F87" s="7">
-        <v>62</v>
+        <v>99</v>
       </c>
       <c r="G87" s="7">
-        <v>52</v>
+        <v>99</v>
       </c>
       <c r="H87" s="7">
         <v>0</v>
@@ -3181,22 +3181,22 @@
         <v>86</v>
       </c>
       <c r="B88" s="3">
+        <v>2</v>
+      </c>
+      <c r="C88" s="3">
         <v>48</v>
       </c>
-      <c r="C88" s="3">
-        <v>2</v>
-      </c>
       <c r="D88" s="7">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="E88" s="7">
-        <v>46</v>
+        <v>99</v>
       </c>
       <c r="F88" s="7">
-        <v>45</v>
+        <v>99</v>
       </c>
       <c r="G88" s="7">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="H88" s="7">
         <v>0</v>
@@ -3212,22 +3212,22 @@
         <v>87</v>
       </c>
       <c r="B89" s="3">
+        <v>0</v>
+      </c>
+      <c r="C89" s="3">
         <v>48</v>
       </c>
-      <c r="C89" s="3">
-        <v>0</v>
-      </c>
       <c r="D89" s="7">
-        <v>22</v>
+        <v>99</v>
       </c>
       <c r="E89" s="7">
-        <v>41</v>
+        <v>99</v>
       </c>
       <c r="F89" s="7">
-        <v>60</v>
+        <v>99</v>
       </c>
       <c r="G89" s="7">
-        <v>53</v>
+        <v>99</v>
       </c>
       <c r="H89" s="7">
         <v>0</v>
@@ -3243,22 +3243,22 @@
         <v>88</v>
       </c>
       <c r="B90" s="3">
+        <v>30</v>
+      </c>
+      <c r="C90" s="3">
         <v>48</v>
       </c>
-      <c r="C90" s="3">
-        <v>3</v>
-      </c>
       <c r="D90" s="7">
-        <v>30</v>
+        <v>99</v>
       </c>
       <c r="E90" s="7">
-        <v>60</v>
+        <v>99</v>
       </c>
       <c r="F90" s="7">
-        <v>60</v>
+        <v>99</v>
       </c>
       <c r="G90" s="7">
-        <v>55</v>
+        <v>99</v>
       </c>
       <c r="H90" s="7">
         <v>0</v>
@@ -3274,22 +3274,22 @@
         <v>89</v>
       </c>
       <c r="B91" s="3">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C91" s="3">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="D91" s="7">
-        <v>29</v>
+        <v>99</v>
       </c>
       <c r="E91" s="7">
-        <v>44</v>
+        <v>99</v>
       </c>
       <c r="F91" s="7">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="G91" s="7">
-        <v>63</v>
+        <v>99</v>
       </c>
       <c r="H91" s="7">
         <v>0</v>
@@ -3305,22 +3305,22 @@
         <v>90</v>
       </c>
       <c r="B92" s="3">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="C92" s="3">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D92" s="7">
-        <v>32</v>
+        <v>99</v>
       </c>
       <c r="E92" s="7">
-        <v>51</v>
+        <v>99</v>
       </c>
       <c r="F92" s="7">
-        <v>45</v>
+        <v>99</v>
       </c>
       <c r="G92" s="7">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="H92" s="7">
         <v>0</v>
@@ -3336,22 +3336,22 @@
         <v>91</v>
       </c>
       <c r="B93" s="3">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="C93" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D93" s="7">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="E93" s="7">
-        <v>45</v>
+        <v>99</v>
       </c>
       <c r="F93" s="7">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="G93" s="7">
-        <v>67</v>
+        <v>99</v>
       </c>
       <c r="H93" s="7">
         <v>0</v>
@@ -3367,22 +3367,22 @@
         <v>92</v>
       </c>
       <c r="B94" s="3">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="C94" s="3">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D94" s="7">
-        <v>31</v>
+        <v>99</v>
       </c>
       <c r="E94" s="7">
-        <v>49</v>
+        <v>99</v>
       </c>
       <c r="F94" s="7">
-        <v>49</v>
+        <v>99</v>
       </c>
       <c r="G94" s="7">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="H94" s="7">
         <v>0</v>
@@ -3398,22 +3398,22 @@
         <v>93</v>
       </c>
       <c r="B95" s="3">
+        <v>0</v>
+      </c>
+      <c r="C95" s="3">
         <v>50</v>
       </c>
-      <c r="C95" s="3">
-        <v>0</v>
-      </c>
       <c r="D95" s="7">
-        <v>31</v>
+        <v>99</v>
       </c>
       <c r="E95" s="7">
-        <v>49</v>
+        <v>99</v>
       </c>
       <c r="F95" s="7">
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="G95" s="7">
-        <v>53</v>
+        <v>99</v>
       </c>
       <c r="H95" s="7">
         <v>0</v>
@@ -3429,22 +3429,22 @@
         <v>94</v>
       </c>
       <c r="B96" s="3">
+        <v>2</v>
+      </c>
+      <c r="C96" s="3">
         <v>48</v>
       </c>
-      <c r="C96" s="3">
-        <v>2</v>
-      </c>
       <c r="D96" s="7">
-        <v>18</v>
+        <v>99</v>
       </c>
       <c r="E96" s="7">
-        <v>48</v>
+        <v>99</v>
       </c>
       <c r="F96" s="7">
-        <v>53</v>
+        <v>99</v>
       </c>
       <c r="G96" s="7">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="H96" s="7">
         <v>0</v>
@@ -3460,22 +3460,22 @@
         <v>95</v>
       </c>
       <c r="B97" s="3">
+        <v>1</v>
+      </c>
+      <c r="C97" s="3">
         <v>37</v>
       </c>
-      <c r="C97" s="3">
-        <v>1</v>
-      </c>
       <c r="D97" s="7">
-        <v>20</v>
+        <v>99</v>
       </c>
       <c r="E97" s="7">
-        <v>45</v>
+        <v>99</v>
       </c>
       <c r="F97" s="7">
-        <v>42</v>
+        <v>99</v>
       </c>
       <c r="G97" s="7">
-        <v>66</v>
+        <v>99</v>
       </c>
       <c r="H97" s="7">
         <v>0</v>
@@ -3491,22 +3491,22 @@
         <v>96</v>
       </c>
       <c r="B98" s="3">
+        <v>0</v>
+      </c>
+      <c r="C98" s="3">
         <v>26</v>
       </c>
-      <c r="C98" s="3">
-        <v>0</v>
-      </c>
       <c r="D98" s="7">
-        <v>32</v>
+        <v>99</v>
       </c>
       <c r="E98" s="7">
-        <v>43</v>
+        <v>99</v>
       </c>
       <c r="F98" s="7">
-        <v>36</v>
+        <v>99</v>
       </c>
       <c r="G98" s="7">
-        <v>57</v>
+        <v>99</v>
       </c>
       <c r="H98" s="7">
         <v>0</v>
@@ -3522,22 +3522,22 @@
         <v>97</v>
       </c>
       <c r="B99" s="3">
+        <v>0</v>
+      </c>
+      <c r="C99" s="3">
         <v>19</v>
       </c>
-      <c r="C99" s="3">
-        <v>0</v>
-      </c>
       <c r="D99" s="7">
-        <v>18</v>
+        <v>99</v>
       </c>
       <c r="E99" s="7">
-        <v>47</v>
+        <v>99</v>
       </c>
       <c r="F99" s="7">
-        <v>35</v>
+        <v>99</v>
       </c>
       <c r="G99" s="7">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="H99" s="7">
         <v>0</v>
@@ -3553,22 +3553,22 @@
         <v>98</v>
       </c>
       <c r="B100" s="3">
+        <v>0</v>
+      </c>
+      <c r="C100" s="3">
         <v>11</v>
       </c>
-      <c r="C100" s="3">
-        <v>0</v>
-      </c>
       <c r="D100" s="7">
-        <v>26</v>
+        <v>99</v>
       </c>
       <c r="E100" s="7">
-        <v>52</v>
+        <v>99</v>
       </c>
       <c r="F100" s="7">
-        <v>32</v>
+        <v>99</v>
       </c>
       <c r="G100" s="7">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="H100" s="7">
         <v>0</v>
@@ -3584,22 +3584,22 @@
         <v>99</v>
       </c>
       <c r="B101" s="3">
+        <v>0</v>
+      </c>
+      <c r="C101" s="3">
         <v>5</v>
       </c>
-      <c r="C101" s="3">
-        <v>0</v>
-      </c>
       <c r="D101" s="7">
-        <v>18</v>
+        <v>99</v>
       </c>
       <c r="E101" s="7">
-        <v>53</v>
+        <v>99</v>
       </c>
       <c r="F101" s="7">
-        <v>45</v>
+        <v>99</v>
       </c>
       <c r="G101" s="7">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="H101" s="7">
         <v>0</v>
@@ -3621,16 +3621,16 @@
         <v>0</v>
       </c>
       <c r="D102" s="7">
-        <v>10</v>
+        <v>99</v>
       </c>
       <c r="E102" s="7">
-        <v>41</v>
+        <v>99</v>
       </c>
       <c r="F102" s="7">
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="G102" s="7">
-        <v>64</v>
+        <v>99</v>
       </c>
       <c r="H102" s="7">
         <v>0</v>
